--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260904.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.61%</t>
+          <t>10.86%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.43%</t>
+          <t>10.32%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.35%</t>
+          <t>8.61%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.56%</t>
+          <t>7.53%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.64%</t>
+          <t>5.53%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.24%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1034,68 +1034,68 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>95,263</t>
+          <t>32,510</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,510</t>
+          <t>95,263</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>30,445</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>30,445</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1210,24 +1210,24 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>75,174</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>75,174</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1342,68 +1342,68 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>30,691</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>30,691</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1474,24 +1474,24 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>119,186,840</t>
+          <t>113,790,053</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
